--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92569022084</v>
+        <v>46157.93101219544</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93101219544</v>
+        <v>46157.93174506948</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93174506948</v>
+        <v>46157.93400806471</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93400806471</v>
+        <v>46157.93718745652</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93718745652</v>
+        <v>46158.2821700005</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821700005</v>
+        <v>46158.2968249132</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2968249132</v>
+        <v>46158.29815502409</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29815502409</v>
+        <v>46158.33388003599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33388003599</v>
+        <v>46158.36857815824</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/12. ИП Лопакова Н.Ф. (аренда транспорта)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36857815824</v>
+        <v>46158.37288441309</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
